--- a/resources/templates/standard/A8101-02.xlsx
+++ b/resources/templates/standard/A8101-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>작성자</t>
   </si>
@@ -759,42 +762,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -811,7 +816,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -824,7 +829,7 @@
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -838,10 +843,10 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
@@ -853,7 +858,7 @@
     </row>
     <row r="4" ht="58.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -867,10 +872,10 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -882,20 +887,20 @@
     </row>
     <row r="5" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -904,22 +909,22 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R5" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>14</v>
       </c>
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
@@ -927,18 +932,18 @@
     </row>
     <row r="6" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -947,25 +952,25 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R6" s="15" t="s">
-        <v>19</v>
-      </c>
       <c r="S6" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T6" s="16"/>
       <c r="U6" s="16"/>
@@ -973,7 +978,7 @@
     <row r="7" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -987,10 +992,10 @@
       <c r="L7" s="4"/>
       <c r="M7" s="14"/>
       <c r="N7" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P7" s="18"/>
       <c r="Q7" s="18"/>
@@ -1002,7 +1007,7 @@
     <row r="8" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1016,10 +1021,10 @@
       <c r="L8" s="4"/>
       <c r="M8" s="14"/>
       <c r="N8" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
@@ -1031,7 +1036,7 @@
     <row r="9" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1045,10 +1050,10 @@
       <c r="L9" s="4"/>
       <c r="M9" s="14"/>
       <c r="N9" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
@@ -1059,7 +1064,7 @@
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -1073,10 +1078,10 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
@@ -1088,7 +1093,7 @@
     </row>
     <row r="11" ht="66" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -1102,10 +1107,10 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -1118,14 +1123,14 @@
     <row r="12" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="22"/>
@@ -1134,16 +1139,16 @@
       <c r="L12" s="4"/>
       <c r="M12" s="9"/>
       <c r="N12" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P12" s="21"/>
       <c r="Q12" s="21"/>
       <c r="R12" s="21"/>
       <c r="S12" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
@@ -1151,7 +1156,7 @@
     <row r="13" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
@@ -1165,10 +1170,10 @@
       <c r="L13" s="4"/>
       <c r="M13" s="9"/>
       <c r="N13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P13" s="21"/>
       <c r="Q13" s="21"/>
@@ -1180,7 +1185,7 @@
     <row r="14" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -1194,10 +1199,10 @@
       <c r="L14" s="4"/>
       <c r="M14" s="9"/>
       <c r="N14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
@@ -1209,7 +1214,7 @@
     <row r="15" ht="76.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -1223,10 +1228,10 @@
       <c r="L15" s="4"/>
       <c r="M15" s="9"/>
       <c r="N15" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
@@ -1237,7 +1242,7 @@
     </row>
     <row r="16" ht="111" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -1251,10 +1256,10 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N16" s="24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
@@ -1289,7 +1294,7 @@
     </row>
     <row r="18" ht="17.25" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
@@ -1303,7 +1308,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N18" s="26"/>
       <c r="O18" s="26"/>
